--- a/04_output/P04/M04_Matriks_Keputusan.xlsx
+++ b/04_output/P04/M04_Matriks_Keputusan.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Decision_Matrix'!$A$1:$G$6</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -41,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123B5D"/>
+        <fgColor rgb="0017365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,7 +53,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D7DEE8"/>
+        <color rgb="00D9E1F2"/>
       </bottom>
     </border>
   </borders>
@@ -433,21 +431,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="39.8" customWidth="1" min="1" max="1"/>
+    <col width="31.4" customWidth="1" min="2" max="2"/>
+    <col width="36.65" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="31.4" customWidth="1" min="5" max="5"/>
+    <col width="18.8" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keputusan</t>
@@ -512,12 +510,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mingguan/bulanan</t>
+          <t>Mingguan/Bulanan</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>B099 orphan; satisfaction null</t>
+          <t>B099 orphan; Satisfaction null</t>
         </is>
       </c>
     </row>
@@ -608,7 +606,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Revenue, Profit, Orders</t>
+          <t>Revenue, Profit, Transactions</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -635,44 +633,41 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bagaimana menangani B099?</t>
+          <t>Produk/kategori mana menekan margin?</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Data Steward / BI</t>
+          <t>Commercial / Product Manager</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Company total vs verified branch analysis</t>
+          <t>Gross Profit, Profit Margin</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Branch_ID, Transaction_ID, Revenue, Profit</t>
+          <t>Product_ID, Category, Revenue, Cost, Profit</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Fact_Sales + Dim_Branch</t>
+          <t>Fact_Sales + Dim_Product</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Saat refresh / audit</t>
+          <t>Bulanan</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Jangan map ke B001-B006 tanpa bukti; pilih Unknown atau Exclude</t>
+          <t>Definisi Profit/Gross Profit harus konsisten; diskon dapat memengaruhi interpretasi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>